--- a/30_table/01_테스트버전/Table_List_Goods.xlsx
+++ b/30_table/01_테스트버전/Table_List_Goods.xlsx
@@ -316,14 +316,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>캐시 100 + 20개</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>캐시 50 + 5개</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>goods_cash_01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -367,14 +359,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>캐시 1000 + 500개</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>캐시 500 + 150개</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>충전 5개</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -911,6 +895,22 @@
   </si>
   <si>
     <t>cha_s_0001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐시 50 + 30개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐시 100 + 100개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐시 500 + 500개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐시 1000 + 1000개</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3533,7 +3533,7 @@
         <v>99999999</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -3719,10 +3719,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D8" s="20" t="s">
         <v>13</v>
@@ -3737,7 +3737,7 @@
         <v>6</v>
       </c>
       <c r="H8" s="26" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
@@ -3753,13 +3753,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E9" s="20">
         <v>0</v>
@@ -3771,7 +3771,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="26" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
@@ -3787,13 +3787,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E10" s="20">
         <v>0</v>
@@ -4007,7 +4007,7 @@
         <v>99999999</v>
       </c>
       <c r="H16" s="26" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -4057,13 +4057,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C18" s="25" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E18" s="25">
         <v>10</v>
@@ -4075,7 +4075,7 @@
         <v>10</v>
       </c>
       <c r="H18" s="39" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -4091,16 +4091,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D19" s="25" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E19" s="25" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F19" s="25">
         <v>0</v>
@@ -4109,7 +4109,7 @@
         <v>32</v>
       </c>
       <c r="H19" s="39" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -4125,16 +4125,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F20" s="25">
         <v>0</v>
@@ -4831,13 +4831,13 @@
         <v>5</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="H1" s="30" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="J1" s="30" t="s">
         <v>64</v>
@@ -4861,34 +4861,34 @@
         <v>36</v>
       </c>
       <c r="Q1" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="R1" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="S1" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="T1" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="U1" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="R1" s="31" t="s">
+      <c r="V1" s="31" t="s">
         <v>118</v>
       </c>
-      <c r="S1" s="31" t="s">
+      <c r="W1" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="T1" s="31" t="s">
+      <c r="X1" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="U1" s="31" t="s">
+      <c r="Y1" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="V1" s="31" t="s">
+      <c r="Z1" s="31" t="s">
         <v>122</v>
-      </c>
-      <c r="W1" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="X1" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="Y1" s="31" t="s">
-        <v>125</v>
-      </c>
-      <c r="Z1" s="31" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.3">
@@ -4899,7 +4899,7 @@
         <v>74</v>
       </c>
       <c r="C2" s="35" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D2" s="33" t="str">
         <f>"STR_"&amp;UPPER(C2)</f>
@@ -4938,7 +4938,7 @@
         <v>10</v>
       </c>
       <c r="P2" s="36" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="Q2" s="33"/>
       <c r="R2" s="33"/>
@@ -4956,10 +4956,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D3" s="33" t="str">
         <f>"STR_"&amp;UPPER(C3)</f>
@@ -5000,7 +5000,7 @@
         <v>20</v>
       </c>
       <c r="P3" s="36" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="Q3" s="33"/>
       <c r="R3" s="33"/>
@@ -5018,10 +5018,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="34" t="s">
+        <v>239</v>
+      </c>
+      <c r="C4" s="35" t="s">
         <v>76</v>
-      </c>
-      <c r="C4" s="35" t="s">
-        <v>78</v>
       </c>
       <c r="D4" s="33" t="str">
         <f t="shared" ref="D4:D11" si="0">"STR_"&amp;UPPER(C4)</f>
@@ -5057,10 +5057,10 @@
         <v>5000</v>
       </c>
       <c r="O4" s="33">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="P4" s="36" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="Q4" s="33"/>
       <c r="R4" s="33"/>
@@ -5078,10 +5078,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>75</v>
+        <v>240</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D5" s="33" t="str">
         <f t="shared" si="0"/>
@@ -5117,10 +5117,10 @@
         <v>10000</v>
       </c>
       <c r="O5" s="33">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="P5" s="36" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="Q5" s="33"/>
       <c r="R5" s="33"/>
@@ -5138,10 +5138,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>90</v>
+        <v>241</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D6" s="33" t="str">
         <f t="shared" si="0"/>
@@ -5177,10 +5177,10 @@
         <v>50000</v>
       </c>
       <c r="O6" s="33">
-        <v>650</v>
+        <v>1000</v>
       </c>
       <c r="P6" s="36" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="Q6" s="33"/>
       <c r="R6" s="33"/>
@@ -5198,10 +5198,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>89</v>
+        <v>242</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D7" s="33" t="str">
         <f t="shared" si="0"/>
@@ -5237,10 +5237,10 @@
         <v>100000</v>
       </c>
       <c r="O7" s="33">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="P7" s="36" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="Q7" s="33"/>
       <c r="R7" s="33"/>
@@ -5258,10 +5258,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D8" s="33" t="str">
         <f t="shared" si="0"/>
@@ -5282,7 +5282,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="33" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K8" s="33">
         <v>1</v>
@@ -5300,7 +5300,7 @@
         <v>10</v>
       </c>
       <c r="P8" s="36" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="Q8" s="33"/>
       <c r="R8" s="33"/>
@@ -5318,10 +5318,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D9" s="33" t="str">
         <f t="shared" si="0"/>
@@ -5342,7 +5342,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="33" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K9" s="33">
         <v>2</v>
@@ -5360,7 +5360,7 @@
         <v>20</v>
       </c>
       <c r="P9" s="36" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="Q9" s="33"/>
       <c r="R9" s="33"/>
@@ -5378,10 +5378,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D10" s="33" t="str">
         <f t="shared" si="0"/>
@@ -5402,7 +5402,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="33" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K10" s="33">
         <v>0</v>
@@ -5420,7 +5420,7 @@
         <v>10</v>
       </c>
       <c r="P10" s="36" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="Q10" s="33"/>
       <c r="R10" s="33"/>
@@ -5438,10 +5438,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D11" s="33" t="str">
         <f t="shared" si="0"/>
@@ -5480,7 +5480,7 @@
         <v>200000</v>
       </c>
       <c r="P11" s="36" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="Q11" s="33"/>
       <c r="R11" s="33"/>
@@ -5498,10 +5498,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D12" s="33" t="str">
         <f t="shared" ref="D12" si="2">"STR_"&amp;UPPER(C12)</f>
@@ -5540,7 +5540,7 @@
         <v>2000000</v>
       </c>
       <c r="P12" s="36" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="Q12" s="33"/>
       <c r="R12" s="33"/>
@@ -5558,10 +5558,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D13" s="33" t="str">
         <f t="shared" ref="D13" si="4">"STR_"&amp;UPPER(C13)</f>
@@ -5600,7 +5600,7 @@
         <v>20000000</v>
       </c>
       <c r="P13" s="36" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="Q13" s="33"/>
       <c r="R13" s="33"/>
@@ -5618,10 +5618,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D14" s="33" t="str">
         <f t="shared" ref="D14:D15" si="6">"STR_"&amp;UPPER(C14)</f>
@@ -5660,7 +5660,7 @@
         <v>5</v>
       </c>
       <c r="P14" s="36" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="Q14" s="33"/>
       <c r="R14" s="33"/>
@@ -5678,10 +5678,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D15" s="33" t="str">
         <f t="shared" si="6"/>
@@ -5720,7 +5720,7 @@
         <v>50</v>
       </c>
       <c r="P15" s="36" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="Q15" s="33"/>
       <c r="R15" s="33"/>
@@ -5738,10 +5738,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="34" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="D16" s="33" t="str">
         <f t="shared" ref="D16" si="8">"STR_"&amp;UPPER(C16)</f>
@@ -5780,7 +5780,7 @@
         <v>500</v>
       </c>
       <c r="P16" s="36" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="Q16" s="33"/>
       <c r="R16" s="33"/>
@@ -5798,10 +5798,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D17" s="33" t="str">
         <f t="shared" ref="D17:D24" si="10">"STR_"&amp;UPPER(C17)</f>
@@ -5822,7 +5822,7 @@
         <v>0</v>
       </c>
       <c r="J17" s="33" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K17" s="33">
         <v>1</v>
@@ -5840,22 +5840,22 @@
         <v>1</v>
       </c>
       <c r="P17" s="36" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q17" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="Q17" s="36" t="s">
+      <c r="R17" s="36" t="s">
+        <v>145</v>
+      </c>
+      <c r="S17" s="36" t="s">
+        <v>146</v>
+      </c>
+      <c r="T17" s="36" t="s">
+        <v>147</v>
+      </c>
+      <c r="U17" s="36" t="s">
         <v>148</v>
-      </c>
-      <c r="R17" s="36" t="s">
-        <v>149</v>
-      </c>
-      <c r="S17" s="36" t="s">
-        <v>150</v>
-      </c>
-      <c r="T17" s="36" t="s">
-        <v>151</v>
-      </c>
-      <c r="U17" s="36" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.3">
@@ -5863,10 +5863,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C18" s="37" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D18" s="33" t="str">
         <f t="shared" si="10"/>
@@ -5887,7 +5887,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="33" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K18" s="33">
         <v>5</v>
@@ -5905,22 +5905,22 @@
         <v>1</v>
       </c>
       <c r="P18" s="36" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="Q18" s="36" t="s">
+        <v>149</v>
+      </c>
+      <c r="R18" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="S18" s="36" t="s">
+        <v>152</v>
+      </c>
+      <c r="T18" s="36" t="s">
         <v>153</v>
       </c>
-      <c r="R18" s="36" t="s">
-        <v>155</v>
-      </c>
-      <c r="S18" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="T18" s="36" t="s">
-        <v>157</v>
-      </c>
       <c r="U18" s="36" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.3">
@@ -5928,10 +5928,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="36" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C19" s="37" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D19" s="33" t="str">
         <f t="shared" si="10"/>
@@ -5952,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="33" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K19" s="33">
         <v>25</v>
@@ -5970,22 +5970,22 @@
         <v>1</v>
       </c>
       <c r="P19" s="36" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="Q19" s="36" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="R19" s="36" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="S19" s="36" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="T19" s="36" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="U19" s="36" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.3">
@@ -5993,10 +5993,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C20" s="37" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D20" s="33" t="str">
         <f t="shared" ref="D20" si="12">"STR_"&amp;UPPER(C20)</f>
@@ -6017,7 +6017,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="33" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K20" s="33">
         <v>125</v>
@@ -6035,22 +6035,22 @@
         <v>1</v>
       </c>
       <c r="P20" s="36" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="Q20" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="R20" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="S20" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="T20" s="36" t="s">
+        <v>164</v>
+      </c>
+      <c r="U20" s="36" t="s">
         <v>165</v>
-      </c>
-      <c r="R20" s="36" t="s">
-        <v>166</v>
-      </c>
-      <c r="S20" s="36" t="s">
-        <v>167</v>
-      </c>
-      <c r="T20" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="U20" s="36" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.3">
@@ -6058,10 +6058,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="36" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C21" s="37" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D21" s="33" t="str">
         <f t="shared" ref="D21" si="14">"STR_"&amp;UPPER(C21)</f>
@@ -6082,7 +6082,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="33" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K21" s="33">
         <v>625</v>
@@ -6100,31 +6100,31 @@
         <v>5</v>
       </c>
       <c r="P21" s="36" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="Q21" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="R21" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="S21" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="T21" s="36" t="s">
+        <v>164</v>
+      </c>
+      <c r="U21" s="36" t="s">
         <v>165</v>
       </c>
-      <c r="R21" s="36" t="s">
-        <v>166</v>
-      </c>
-      <c r="S21" s="36" t="s">
-        <v>167</v>
-      </c>
-      <c r="T21" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="U21" s="36" t="s">
-        <v>169</v>
-      </c>
       <c r="V21" s="36" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="W21" s="36" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="X21" s="36" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.3">
@@ -6132,10 +6132,10 @@
         <v>20</v>
       </c>
       <c r="B22" s="34" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D22" s="33" t="str">
         <f t="shared" si="10"/>
@@ -6156,7 +6156,7 @@
         <v>0</v>
       </c>
       <c r="J22" s="33" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K22" s="33">
         <v>3</v>
@@ -6174,10 +6174,10 @@
         <v>1</v>
       </c>
       <c r="P22" s="36" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="Q22" s="36" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.3">
@@ -6185,10 +6185,10 @@
         <v>21</v>
       </c>
       <c r="B23" s="36" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C23" s="37" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D23" s="33" t="str">
         <f t="shared" si="10"/>
@@ -6209,7 +6209,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="33" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K23" s="33">
         <v>3</v>
@@ -6227,10 +6227,10 @@
         <v>1</v>
       </c>
       <c r="P23" s="36" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="Q23" s="36" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.3">
@@ -6238,10 +6238,10 @@
         <v>22</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C24" s="37" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D24" s="33" t="str">
         <f t="shared" si="10"/>
@@ -6262,7 +6262,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="33" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K24" s="33">
         <v>3</v>
@@ -6280,10 +6280,10 @@
         <v>1</v>
       </c>
       <c r="P24" s="36" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="Q24" s="36" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.3">
@@ -6291,10 +6291,10 @@
         <v>23</v>
       </c>
       <c r="B25" s="36" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C25" s="37" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D25" s="33" t="str">
         <f t="shared" ref="D25:D29" si="16">"STR_"&amp;UPPER(C25)</f>
@@ -6315,7 +6315,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="33" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K25" s="33">
         <v>3</v>
@@ -6333,10 +6333,10 @@
         <v>1</v>
       </c>
       <c r="P25" s="36" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="Q25" s="36" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.3">
@@ -6344,10 +6344,10 @@
         <v>24</v>
       </c>
       <c r="B26" s="36" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D26" s="33" t="str">
         <f t="shared" si="16"/>
@@ -6368,7 +6368,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="33" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K26" s="33">
         <v>3</v>
@@ -6386,10 +6386,10 @@
         <v>1</v>
       </c>
       <c r="P26" s="36" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="Q26" s="36" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.3">
@@ -6397,10 +6397,10 @@
         <v>25</v>
       </c>
       <c r="B27" s="34" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C27" s="37" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D27" s="33" t="str">
         <f t="shared" si="16"/>
@@ -6421,7 +6421,7 @@
         <v>1</v>
       </c>
       <c r="J27" s="33" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K27" s="33">
         <v>15</v>
@@ -6439,10 +6439,10 @@
         <v>1</v>
       </c>
       <c r="P27" s="36" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="Q27" s="36" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.3">
@@ -6450,10 +6450,10 @@
         <v>26</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C28" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D28" s="33" t="str">
         <f t="shared" si="16"/>
@@ -6474,7 +6474,7 @@
         <v>1</v>
       </c>
       <c r="J28" s="33" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K28" s="33">
         <v>15</v>
@@ -6492,10 +6492,10 @@
         <v>1</v>
       </c>
       <c r="P28" s="36" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="Q28" s="36" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.3">
@@ -6503,10 +6503,10 @@
         <v>27</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C29" s="37" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D29" s="33" t="str">
         <f t="shared" si="16"/>
@@ -6527,7 +6527,7 @@
         <v>1</v>
       </c>
       <c r="J29" s="33" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K29" s="33">
         <v>15</v>
@@ -6545,10 +6545,10 @@
         <v>1</v>
       </c>
       <c r="P29" s="36" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="Q29" s="36" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.3">
@@ -6556,10 +6556,10 @@
         <v>28</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C30" s="37" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D30" s="33" t="str">
         <f t="shared" ref="D30:D34" si="18">"STR_"&amp;UPPER(C30)</f>
@@ -6580,7 +6580,7 @@
         <v>1</v>
       </c>
       <c r="J30" s="33" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K30" s="33">
         <v>15</v>
@@ -6598,10 +6598,10 @@
         <v>1</v>
       </c>
       <c r="P30" s="36" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="Q30" s="36" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.3">
@@ -6609,10 +6609,10 @@
         <v>29</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C31" s="37" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D31" s="33" t="str">
         <f t="shared" si="18"/>
@@ -6633,7 +6633,7 @@
         <v>1</v>
       </c>
       <c r="J31" s="33" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K31" s="33">
         <v>15</v>
@@ -6651,10 +6651,10 @@
         <v>1</v>
       </c>
       <c r="P31" s="36" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="Q31" s="36" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.3">
@@ -6662,10 +6662,10 @@
         <v>30</v>
       </c>
       <c r="B32" s="34" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C32" s="37" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D32" s="33" t="str">
         <f t="shared" si="18"/>
@@ -6686,7 +6686,7 @@
         <v>2</v>
       </c>
       <c r="J32" s="33" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K32" s="33">
         <v>75</v>
@@ -6704,10 +6704,10 @@
         <v>1</v>
       </c>
       <c r="P32" s="36" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="Q32" s="36" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.3">
@@ -6715,10 +6715,10 @@
         <v>31</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C33" s="37" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D33" s="33" t="str">
         <f t="shared" si="18"/>
@@ -6739,7 +6739,7 @@
         <v>2</v>
       </c>
       <c r="J33" s="33" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K33" s="33">
         <v>75</v>
@@ -6757,10 +6757,10 @@
         <v>1</v>
       </c>
       <c r="P33" s="36" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="Q33" s="36" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.3">
@@ -6768,10 +6768,10 @@
         <v>32</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C34" s="37" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D34" s="33" t="str">
         <f t="shared" si="18"/>
@@ -6792,7 +6792,7 @@
         <v>2</v>
       </c>
       <c r="J34" s="33" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K34" s="33">
         <v>75</v>
@@ -6810,10 +6810,10 @@
         <v>1</v>
       </c>
       <c r="P34" s="36" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="Q34" s="36" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.3">
@@ -6821,10 +6821,10 @@
         <v>33</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C35" s="37" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D35" s="33" t="str">
         <f t="shared" ref="D35:D36" si="20">"STR_"&amp;UPPER(C35)</f>
@@ -6845,7 +6845,7 @@
         <v>2</v>
       </c>
       <c r="J35" s="33" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K35" s="33">
         <v>75</v>
@@ -6863,10 +6863,10 @@
         <v>1</v>
       </c>
       <c r="P35" s="36" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="Q35" s="36" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.3">
@@ -6874,10 +6874,10 @@
         <v>34</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C36" s="37" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D36" s="33" t="str">
         <f t="shared" si="20"/>
@@ -6898,7 +6898,7 @@
         <v>2</v>
       </c>
       <c r="J36" s="33" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K36" s="33">
         <v>75</v>
@@ -6916,10 +6916,10 @@
         <v>1</v>
       </c>
       <c r="P36" s="36" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="Q36" s="36" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -6959,7 +6959,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -6981,7 +6981,7 @@
         <v>47</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -7003,7 +7003,7 @@
         <v>53</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -7025,7 +7025,7 @@
         <v>49</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -7047,7 +7047,7 @@
         <v>51</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -7069,7 +7069,7 @@
         <v>55</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
